--- a/Current TAPPs/SEM_Imaging_TAPP_v29.xlsx
+++ b/Current TAPPs/SEM_Imaging_TAPP_v29.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legends" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legends" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -616,7 +616,7 @@
           <t>Keyed By</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
@@ -924,7 +924,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="1" t="n"/>
       <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1088,7 +1088,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="1" t="n"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1252,7 +1252,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="1" t="n"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1416,7 +1416,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="1" t="n"/>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1580,7 +1580,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="1" t="n"/>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1744,7 +1744,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="1" t="n"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1908,7 +1908,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="1" t="n"/>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2072,7 +2072,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="1" t="n"/>
       <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2236,7 +2236,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Encourages formal procedure registration and ensures traceability.</t>
         </is>
@@ -2400,7 +2400,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session, which may cover several samples, and this is the link back to the raw instrument files.</t>
         </is>
@@ -2496,7 +2496,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="1" t="n"/>
       <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2660,7 +2660,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="1" t="n"/>
       <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2824,7 +2824,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="1" t="n"/>
       <c r="K15" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2988,7 +2988,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="1" t="n"/>
       <c r="K16" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3152,7 +3152,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="1" t="n"/>
       <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3316,7 +3316,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="1" t="n"/>
       <c r="K18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3480,7 +3480,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>Provides a stable, citable link to the companion method independent of whether a dataset has been deposited.</t>
         </is>
@@ -3648,7 +3648,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="1" t="n"/>
       <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3948,7 +3948,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>Used for discoverability and procedure matching, and because the material type constrains sample preparation, calibration and matrix-matching requirements.</t>
         </is>
@@ -4116,7 +4116,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n"/>
+      <c r="J23" s="1" t="n"/>
       <c r="K23" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4280,7 +4280,7 @@
           <t>defines: sample</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session and may cover several samples.</t>
         </is>
@@ -4448,7 +4448,7 @@
           <t>defines: sampling unit</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
+      <c r="J25" s="1" t="n"/>
       <c r="K25" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4540,7 +4540,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
+      <c r="J26" s="1" t="n"/>
       <c r="K26" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4700,7 +4700,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
+      <c r="J27" s="1" t="n"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4788,7 +4788,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
+      <c r="J28" s="1" t="n"/>
       <c r="K28" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5016,7 +5016,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="1" t="inlineStr">
         <is>
           <t>Recording it as a controlled value lets procedures be found by vendor.</t>
         </is>
@@ -5184,7 +5184,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="1" t="n"/>
       <c r="K31" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5344,7 +5344,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
+      <c r="J32" s="1" t="n"/>
       <c r="K32" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5504,7 +5504,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n"/>
+      <c r="J33" s="1" t="n"/>
       <c r="K33" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5664,7 +5664,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
+      <c r="J34" s="1" t="n"/>
       <c r="K34" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5824,7 +5824,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>Solid-state diode detectors (single or segmented) are standard; YAG scintillator detectors offer high sensitivity at low voltage. In-lens BSE detectors provide improved BSE collection at short working distances.</t>
         </is>
@@ -5988,7 +5988,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n"/>
+      <c r="J36" s="1" t="n"/>
       <c r="K36" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -6148,7 +6148,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J37" s="2" t="n"/>
+      <c r="J37" s="1" t="n"/>
       <c r="K37" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -6312,7 +6312,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J38" s="2" t="n"/>
+      <c r="J38" s="1" t="n"/>
       <c r="K38" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6476,7 +6476,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="n"/>
+      <c r="J39" s="1" t="n"/>
       <c r="K39" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6776,7 +6776,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability. Ensures every procedure record is self-describing and comparable across the library.</t>
         </is>
@@ -6944,7 +6944,7 @@
           <t>defines: reported property</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>A procedure may acquire many channels and report a small number of derived quantities; without this field a data consumer cannot tell which.</t>
         </is>
@@ -7036,7 +7036,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>Affects X-ray generation depth (EDS/WDS), EBSD pattern quality, imaging resolution, and beam penetration. Low voltages (1-5 kV) improve surface sensitivity and reduce beam damage; high voltages (15-20 kV) improve X-ray generation for quantitative analysis.</t>
         </is>
@@ -7200,7 +7200,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr">
         <is>
           <t>Higher current improves signal-to-noise for X-ray analysis (EDS/WDS, EBSD) and CL but may increase beam damage and reduce spatial resolution.</t>
         </is>
@@ -7364,7 +7364,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>Affects spatial resolution, depth of focus, EDS X-ray take-off angle, and EBSD geometry.</t>
         </is>
@@ -7528,7 +7528,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J46" s="2" t="n"/>
+      <c r="J46" s="1" t="n"/>
       <c r="K46" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7688,7 +7688,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>Defines spatial sampling of SE or BSE images.</t>
         </is>
@@ -7852,7 +7852,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="1" t="inlineStr">
         <is>
           <t>Longer dwell time improves signal-to-noise and counting statistics but increases total dose and can cause beam damage or contamination on sensitive materials.</t>
         </is>
@@ -8016,7 +8016,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n"/>
+      <c r="J49" s="1" t="n"/>
       <c r="K49" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -8176,7 +8176,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr">
         <is>
           <t>The range is set by the detector sensitivity and any optical filters installed.</t>
         </is>
@@ -8340,7 +8340,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J51" s="2" t="n"/>
+      <c r="J51" s="1" t="n"/>
       <c r="K51" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -8500,7 +8500,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr">
         <is>
           <t>Longer integration improves signal-to-noise but increases beam dose and acquisition time.</t>
         </is>
@@ -8664,7 +8664,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J53" s="1" t="inlineStr">
         <is>
           <t>Standard EBSD geometry uses 70 degrees tilt toward the EBSD camera to maximise diffracted electron signal.</t>
         </is>
@@ -8828,7 +8828,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr">
         <is>
           <t>Only then are grain boundary positions and intragrain orientation gradients resolved.</t>
         </is>
@@ -8992,7 +8992,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="1" t="inlineStr">
         <is>
           <t>Longer frame time improves pattern quality and indexing rate but increases total acquisition time.</t>
         </is>
@@ -9156,7 +9156,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J56" s="2" t="n"/>
+      <c r="J56" s="1" t="n"/>
       <c r="K56" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -9452,7 +9452,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J58" s="2" t="n"/>
+      <c r="J58" s="1" t="n"/>
       <c r="K58" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -9612,7 +9612,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J59" s="2" t="n"/>
+      <c r="J59" s="1" t="n"/>
       <c r="K59" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -9772,7 +9772,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J60" s="2" t="n"/>
+      <c r="J60" s="1" t="n"/>
       <c r="K60" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -9936,7 +9936,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J61" s="2" t="n"/>
+      <c r="J61" s="1" t="n"/>
       <c r="K61" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10160,7 +10160,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="1" t="inlineStr">
         <is>
           <t>Values above ~1.5 degrees typically indicate unreliable indexing.</t>
         </is>
@@ -10324,7 +10324,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="1" t="inlineStr">
         <is>
           <t>Low indexing rate may indicate surface damage, amorphisation, severe deformation, or phase misidentification.</t>
         </is>
@@ -10488,7 +10488,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J65" s="2" t="n"/>
+      <c r="J65" s="1" t="n"/>
       <c r="K65" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -10652,7 +10652,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J66" s="2" t="n"/>
+      <c r="J66" s="1" t="n"/>
       <c r="K66" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10781,7 +10781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10905,7 +10905,7 @@
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>SE Imaging</t>
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
@@ -10913,7 +10913,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>SE Imaging</t>
+          <t>BSE Imaging</t>
         </is>
       </c>
       <c r="B10" s="1" t="n"/>
@@ -10921,7 +10921,7 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>BSE Imaging</t>
+          <t>CL Point Analysis</t>
         </is>
       </c>
       <c r="B11" s="1" t="n"/>
@@ -10929,7 +10929,7 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>CL Point Analysis</t>
+          <t>CL Mapping</t>
         </is>
       </c>
       <c r="B12" s="1" t="n"/>
@@ -10937,194 +10937,186 @@
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>CL Mapping</t>
+          <t>EBSD</t>
         </is>
       </c>
       <c r="B13" s="1" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>EBSD</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n"/>
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>This field applies to this analytical mode and should be reported.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>This field applies to this analytical mode and should be reported.</t>
+          <t>This field does not apply to this analytical mode.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>This field does not apply to this analytical mode.</t>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>What to enter</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>What to enter</t>
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Controlled list</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>Controlled list</t>
+          <t>Controlled list / Text</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
+          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>Controlled list / Text</t>
+          <t>Numeric (unit)</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
+          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>Numeric (unit)</t>
+          <t>Numeric + unit</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
+          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>Numeric + unit</t>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
+          <t>Free text. No controlled vocabulary applies.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>N/A | None</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Free text. No controlled vocabulary applies.</t>
+          <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>N/A | None</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Keyed By (Rule 7)</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>What the field's value repeats over</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Keyed By (Rule 7)</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>What the field's value repeats over</t>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>Scalar — one value per procedure or analysis. The default.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>defines: reported property</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Scalar — one value per procedure or analysis. The default.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>defines: reported property</t>
+          <t>defines: sample</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
+          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>defines: sample</t>
+          <t>defines: sampling unit</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>defines: sampling unit</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
